--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486898_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486898_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3638</v>
+        <v>1.6365</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3184</v>
+        <v>0.4428</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0454</v>
+        <v>1.1936</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1873</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1137</v>
+        <v>0.3864</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1776</v>
+        <v>0.302</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0638</v>
+        <v>0.0844</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4269</v>
+        <v>-0.2111</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1822</v>
+        <v>0.4573</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6091</v>
+        <v>-0.6684</v>
       </c>
       <c r="G3" t="n">
         <v>-2.2828</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5897</v>
+        <v>-0.3739</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7905</v>
+        <v>-0.5154</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2008</v>
+        <v>0.1415</v>
       </c>
       <c r="V3" t="n">
         <v>1.4189</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.9981</v>
+        <v>-1.504</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3709</v>
+        <v>-1.1733</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6271</v>
+        <v>-0.3307</v>
       </c>
       <c r="G4" t="n">
         <v>1.0095</v>
@@ -766,13 +766,13 @@
         <v>2.4641</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9726</v>
+        <v>-0.4786</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.3411</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4339</v>
+        <v>-0.1374</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4189</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.2722</v>
+        <v>-1.7343</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.254</v>
+        <v>-2.39</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9818</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-2.5589</v>
@@ -844,13 +844,13 @@
         <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6435</v>
+        <v>-0.1056</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1625</v>
+        <v>-0.2986</v>
       </c>
       <c r="U5" t="n">
-        <v>0.519</v>
+        <v>0.1929</v>
       </c>
       <c r="V5" t="n">
         <v>0.1088</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.5151</v>
+        <v>-1.8446</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.7656</v>
+        <v>-3.0062</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2505</v>
+        <v>1.1616</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6847</v>
@@ -922,13 +922,13 @@
         <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2492</v>
+        <v>0.4213</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6355</v>
+        <v>0.1238</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3864</v>
+        <v>0.2974</v>
       </c>
       <c r="V6" t="n">
         <v>0.2402</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5771</v>
+        <v>-3.1776</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5826</v>
+        <v>-4.1831</v>
       </c>
       <c r="F7" t="n">
         <v>1.0055</v>
@@ -1000,10 +1000,10 @@
         <v>2.2588</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4915</v>
+        <v>0.891</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9295</v>
+        <v>0.3291</v>
       </c>
       <c r="U7" t="n">
         <v>0.5619</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>D. JACKSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1967</v>
+        <v>-3.4257</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.9415</v>
+        <v>-4.3277</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7448</v>
+        <v>0.902</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.537</v>
+        <v>-3.7528</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8848</v>
+        <v>-2.0662</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6522</v>
+        <v>-1.6867</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1965</v>
+        <v>-2.801</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4463</v>
+        <v>-1.4852</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7502</v>
+        <v>-1.3158</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3405</v>
+        <v>-0.9519</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4385</v>
+        <v>-0.581</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.902</v>
+        <v>-0.3709</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
         <v>2.6694</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9502</v>
+        <v>0.1916</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5343</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4159</v>
+        <v>-0.3351</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0472</v>
+        <v>-0.4805</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0472</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. TRAORE</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8214</v>
+        <v>-3.4331</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6245</v>
+        <v>-4.2669</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1968</v>
+        <v>0.8337</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.3625</v>
+        <v>-4.537</v>
       </c>
       <c r="H9" t="n">
-        <v>0.545</v>
+        <v>-1.8848</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.9075</v>
+        <v>-2.6522</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3454</v>
+        <v>-2.1965</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6809</v>
+        <v>-1.4463</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.0262</v>
+        <v>-0.7502</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0171</v>
+        <v>-2.3405</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1358</v>
+        <v>-0.4385</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8813</v>
+        <v>-1.902</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
         <v>2.6694</v>
       </c>
       <c r="S9" t="n">
-        <v>0.535</v>
+        <v>0.7137</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0268</v>
+        <v>0.2089</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5081</v>
+        <v>0.5048</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6366</v>
+        <v>-1.0472</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7207</v>
+        <v>-1.0472</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. JACKSON</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2583</v>
+        <v>-3.9001</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9825</v>
+        <v>-4.8599</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7242</v>
+        <v>0.9598</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.7528</v>
+        <v>-4.5538</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0662</v>
+        <v>-0.6199</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6867</v>
+        <v>-3.9339</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.801</v>
+        <v>-3.7943</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4852</v>
+        <v>-0.347</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3158</v>
+        <v>-3.4473</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9519</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.581</v>
+        <v>-0.2729</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3709</v>
+        <v>-0.4866</v>
       </c>
       <c r="P10" t="n">
         <v>0.616</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6694</v>
+        <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.641</v>
+        <v>0.0377</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1281</v>
+        <v>-0.0389</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5129</v>
+        <v>0.0766</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>B. TRAORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5845</v>
+        <v>-4.3748</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5147</v>
+        <v>-2.9112</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9302</v>
+        <v>-1.4636</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.5538</v>
+        <v>-4.3625</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6199</v>
+        <v>0.545</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.9339</v>
+        <v>-4.9075</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7943</v>
+        <v>-2.3454</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.347</v>
+        <v>1.6809</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.4473</v>
+        <v>-4.0262</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-2.0171</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2729</v>
+        <v>-1.1358</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4866</v>
+        <v>-0.8813</v>
       </c>
       <c r="P11" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6427</v>
+        <v>2.6694</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.0185</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6937</v>
+        <v>-0.2598</v>
       </c>
       <c r="U11" t="n">
-        <v>0.047</v>
+        <v>0.2413</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.6366</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-23.2865</v>
+        <v>-21.9688</v>
       </c>
       <c r="E12" t="n">
-        <v>-27.5357</v>
+        <v>-26.2182</v>
       </c>
       <c r="F12" t="n">
-        <v>4.249400000000001</v>
+        <v>4.2492</v>
       </c>
       <c r="G12" t="n">
         <v>-27.9173</v>
@@ -1366,7 +1366,7 @@
         <v>-14.2832</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.1105</v>
+        <v>-3.110499999999999</v>
       </c>
       <c r="L12" t="n">
         <v>-11.1729</v>
@@ -1378,7 +1378,7 @@
         <v>-6.913399999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.720799999999999</v>
+        <v>-6.720800000000001</v>
       </c>
       <c r="P12" t="n">
         <v>6.1602</v>
@@ -1390,13 +1390,13 @@
         <v>20.5341</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3477000000000001</v>
+        <v>1.6651</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2809</v>
+        <v>0.03669999999999995</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6285</v>
+        <v>1.6283</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8769</v>
@@ -1405,7 +1405,7 @@
         <v>2.4023</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.2792</v>
+        <v>-4.279199999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.6243</v>
+        <v>8.427099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5758</v>
+        <v>3.308</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0485</v>
+        <v>5.1191</v>
       </c>
       <c r="G13" t="n">
         <v>6.9683</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.576</v>
+        <v>0.2268</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1198</v>
+        <v>-0.3876</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4562</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4996</v>
+        <v>7.2579</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5237</v>
+        <v>1.7329</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9759</v>
+        <v>5.525</v>
       </c>
       <c r="G14" t="n">
         <v>2.5781</v>
@@ -1546,13 +1546,13 @@
         <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.366</v>
+        <v>0.3924</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.283</v>
+        <v>-0.0738</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.083</v>
+        <v>0.4662</v>
       </c>
       <c r="V14" t="n">
         <v>3.0554</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.54</v>
+        <v>6.1635</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4285</v>
+        <v>-0.4563</v>
       </c>
       <c r="F15" t="n">
-        <v>5.9685</v>
+        <v>6.6198</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4134</v>
+        <v>7.0604</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1133</v>
+        <v>3.9028</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3001</v>
+        <v>3.1576</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6862</v>
+        <v>4.6697</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4099</v>
+        <v>4.1175</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2763</v>
+        <v>0.5522</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7272</v>
+        <v>2.3907</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7034</v>
+        <v>-0.2147</v>
       </c>
       <c r="O15" t="n">
-        <v>2.0238</v>
+        <v>2.6055</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.0801</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q15" t="n">
         <v>-5.1336</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0534</v>
+        <v>2.6694</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5558</v>
+        <v>0.3885</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5384</v>
+        <v>-0.4729</v>
       </c>
       <c r="U15" t="n">
-        <v>2.0175</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3491</v>
+        <v>1.1786</v>
       </c>
       <c r="W15" t="n">
         <v>0.4805</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8295</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5404</v>
+        <v>4.6891</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2931</v>
+        <v>-0.8469</v>
       </c>
       <c r="F16" t="n">
-        <v>5.8335</v>
+        <v>5.5361</v>
       </c>
       <c r="G16" t="n">
-        <v>7.0604</v>
+        <v>6.4134</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9028</v>
+        <v>4.1133</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1576</v>
+        <v>2.3001</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6697</v>
+        <v>3.6862</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1175</v>
+        <v>3.4099</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5522</v>
+        <v>0.2763</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3907</v>
+        <v>2.7272</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2147</v>
+        <v>0.7034</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6055</v>
+        <v>2.0238</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.4641</v>
+        <v>-3.0801</v>
       </c>
       <c r="Q16" t="n">
         <v>-5.1336</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6694</v>
+        <v>2.0534</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2346</v>
+        <v>1.7049</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3097</v>
+        <v>0.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0751</v>
+        <v>1.585</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1786</v>
+        <v>-0.3491</v>
       </c>
       <c r="W16" t="n">
         <v>0.4805</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6982</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0198</v>
+        <v>3.3154</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.158</v>
+        <v>-3.2041</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1778</v>
+        <v>6.5195</v>
       </c>
       <c r="G17" t="n">
         <v>4.8843</v>
@@ -1780,13 +1780,13 @@
         <v>2.2588</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0102</v>
+        <v>1.3058</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4411</v>
+        <v>0.395</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5692</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8551</v>
+        <v>1.1689</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2109</v>
+        <v>-0.3156</v>
       </c>
       <c r="F18" t="n">
-        <v>1.066</v>
+        <v>1.4844</v>
       </c>
       <c r="G18" t="n">
         <v>1.5335</v>
@@ -1858,13 +1858,13 @@
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4997</v>
+        <v>-0.1859</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4147</v>
+        <v>-0.5193</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.3334</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5893</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>R. ROTCENKOVS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7514</v>
+        <v>-0.6795</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7697</v>
+        <v>-0.8166</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0184</v>
+        <v>0.1371</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1554</v>
+        <v>-0.4557</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2448</v>
+        <v>-0.6584</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0893</v>
+        <v>0.2027</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.0796</v>
+        <v>-0.619</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.0531</v>
+        <v>-0.6584</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0264</v>
+        <v>0.0395</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9241</v>
+        <v>0.1632</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1917</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1158</v>
+        <v>0.1632</v>
       </c>
       <c r="P19" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2119</v>
+        <v>-0.1889</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3098</v>
+        <v>-0.1976</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5218</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. ROTCENKOVS</t>
+          <t>T. TRIFONOV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,31 +1969,31 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7684</v>
+        <v>-0.7245</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8166</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0481</v>
+        <v>-0.8013</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4557</v>
+        <v>1.4256</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6584</v>
+        <v>0.0389</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2027</v>
+        <v>1.3867</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.619</v>
+        <v>1.2624</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6584</v>
+        <v>0.0389</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>1.2234</v>
       </c>
       <c r="M20" t="n">
         <v>0.1632</v>
@@ -2005,37 +2005,37 @@
         <v>0.1632</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2053</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2778</v>
+        <v>-0.1501</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1976</v>
+        <v>-0.1589</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. TRIFONOV</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9181</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0278</v>
+        <v>-2.1881</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8903</v>
+        <v>1.3862</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4256</v>
+        <v>-1.1554</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0389</v>
+        <v>-2.2448</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3867</v>
+        <v>1.0893</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2624</v>
+        <v>-2.0796</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0389</v>
+        <v>-2.0531</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2234</v>
+        <v>-0.0264</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1632</v>
+        <v>0.9241</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.1917</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1632</v>
+        <v>1.1158</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3437</v>
+        <v>-0.2625</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2635</v>
+        <v>-0.1086</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.1539</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.355</v>
+        <v>-2.0429</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6441</v>
+        <v>-1.5395</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7109</v>
+        <v>-0.5034</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3349</v>
@@ -2170,13 +2170,13 @@
         <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4041</v>
+        <v>-0.092</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3294</v>
+        <v>-0.2248</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0747</v>
+        <v>0.1328</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>23.2863</v>
+        <v>26.7731</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2492</v>
+        <v>-4.249400000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>27.5355</v>
+        <v>31.0225</v>
       </c>
       <c r="G23" t="n">
         <v>27.9176</v>
@@ -2224,7 +2224,7 @@
         <v>13.6342</v>
       </c>
       <c r="K23" t="n">
-        <v>6.913399999999999</v>
+        <v>6.913399999999998</v>
       </c>
       <c r="L23" t="n">
         <v>6.7209</v>
@@ -2248,13 +2248,13 @@
         <v>14.3739</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3477999999999999</v>
+        <v>3.139</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6284</v>
+        <v>-1.6285</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2807</v>
+        <v>4.7675</v>
       </c>
       <c r="V23" t="n">
         <v>1.8768</v>
